--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:47</t>
+    <t xml:space="preserve">2026-09-24 00:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,7 +487,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-10</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-90</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-107</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="5">
@@ -538,7 +538,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-5149</v>
+        <v>-2161</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:25</t>
+    <t xml:space="preserve">2026-09-27 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:14</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:25</t>
+    <t xml:space="preserve">2026-10-05 08:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
